--- a/plate3d/PLATE3D_HBASE.xlsx
+++ b/plate3d/PLATE3D_HBASE.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="93">
   <si>
     <t>HAUNCHED BOX BASE - every plate at its scheduled size, thickness and count</t>
   </si>
@@ -94,13 +94,13 @@
     <t>pl.hvt3</t>
   </si>
   <si>
-    <t>PL HADD1 10T  2 EA/SET  - 142x50</t>
+    <t>PL HADD1 10T  1 EA/SET  - 142x50, the bracket end plate</t>
   </si>
   <si>
     <t>pl.hadd1</t>
   </si>
   <si>
-    <t>PL HADD2 10T  2 EA/SET  - 100x40</t>
+    <t>PL HADD2 10T  2 EA/SET  - 100x40, the two ribs under it</t>
   </si>
   <si>
     <t>pl.hadd2</t>
@@ -238,16 +238,16 @@
     <t>pl.hsl_3</t>
   </si>
   <si>
+    <t>pl.hadd2_1</t>
+  </si>
+  <si>
+    <t>br</t>
+  </si>
+  <si>
+    <t>pl.hadd2_2</t>
+  </si>
+  <si>
     <t>pl.hadd1_1</t>
-  </si>
-  <si>
-    <t>pl.hadd1_2</t>
-  </si>
-  <si>
-    <t>pl.hadd2_1</t>
-  </si>
-  <si>
-    <t>pl.hadd2_2</t>
   </si>
   <si>
     <t>BASE</t>
@@ -683,7 +683,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L45"/>
+  <dimension ref="A1:L44"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="66" customWidth="1"/>
@@ -1612,28 +1612,28 @@
         <v>75</v>
       </c>
       <c r="E35" t="s">
-        <v>16</v>
+        <v>76</v>
       </c>
       <c r="F35">
-        <v>-96</v>
+        <v>-71</v>
       </c>
       <c r="G35">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H35">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="I35" t="s">
-        <v>61</v>
-      </c>
-      <c r="J35">
-        <v>0</v>
-      </c>
-      <c r="K35">
-        <v>0</v>
-      </c>
-      <c r="L35">
-        <v>90</v>
+        <v>63</v>
+      </c>
+      <c r="J35" t="s">
+        <v>34</v>
+      </c>
+      <c r="K35" t="s">
+        <v>34</v>
+      </c>
+      <c r="L35" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
@@ -1647,31 +1647,31 @@
         <v>60</v>
       </c>
       <c r="D36" t="s">
+        <v>77</v>
+      </c>
+      <c r="E36" t="s">
         <v>76</v>
       </c>
-      <c r="E36" t="s">
-        <v>16</v>
-      </c>
       <c r="F36">
-        <v>-96</v>
+        <v>-71</v>
       </c>
       <c r="G36">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="H36">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I36" t="s">
-        <v>61</v>
-      </c>
-      <c r="J36">
-        <v>0</v>
-      </c>
-      <c r="K36">
-        <v>0</v>
-      </c>
-      <c r="L36">
-        <v>90</v>
+        <v>63</v>
+      </c>
+      <c r="J36" t="s">
+        <v>34</v>
+      </c>
+      <c r="K36" t="s">
+        <v>34</v>
+      </c>
+      <c r="L36" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
@@ -1685,19 +1685,19 @@
         <v>60</v>
       </c>
       <c r="D37" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E37" t="s">
         <v>31</v>
       </c>
       <c r="F37">
-        <v>-116</v>
+        <v>-176</v>
       </c>
       <c r="G37">
         <v>0</v>
       </c>
       <c r="H37">
-        <v>145</v>
+        <v>0</v>
       </c>
       <c r="I37" t="s">
         <v>66</v>
@@ -1712,141 +1712,103 @@
         <v>34</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C38" t="s">
-        <v>60</v>
-      </c>
-      <c r="D38" t="s">
-        <v>78</v>
-      </c>
-      <c r="E38" t="s">
-        <v>31</v>
-      </c>
-      <c r="F38">
-        <v>-116</v>
-      </c>
-      <c r="G38">
-        <v>0</v>
-      </c>
-      <c r="H38">
-        <v>65</v>
-      </c>
-      <c r="I38" t="s">
-        <v>66</v>
-      </c>
-      <c r="J38" t="s">
-        <v>34</v>
-      </c>
-      <c r="K38" t="s">
-        <v>34</v>
-      </c>
-      <c r="L38" t="s">
-        <v>34</v>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C39" t="s">
+        <v>2</v>
+      </c>
+      <c r="D39" t="s">
+        <v>79</v>
+      </c>
+      <c r="E39" t="s">
+        <v>52</v>
+      </c>
+      <c r="F39" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B40" s="2" t="s">
-        <v>51</v>
+      <c r="B40" s="3" t="s">
+        <v>59</v>
       </c>
       <c r="C40" t="s">
-        <v>2</v>
+        <v>60</v>
       </c>
       <c r="D40" t="s">
         <v>79</v>
       </c>
       <c r="E40" t="s">
-        <v>52</v>
+        <v>13</v>
       </c>
       <c r="F40" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C41" t="s">
-        <v>60</v>
-      </c>
-      <c r="D41" t="s">
-        <v>79</v>
-      </c>
-      <c r="E41" t="s">
-        <v>13</v>
-      </c>
-      <c r="F41" t="s">
         <v>81</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C42" t="s">
+        <v>2</v>
+      </c>
+      <c r="D42" t="s">
+        <v>84</v>
+      </c>
+      <c r="E42" t="s">
+        <v>85</v>
+      </c>
+      <c r="F42" t="s">
+        <v>86</v>
+      </c>
+      <c r="G42" t="s">
+        <v>87</v>
+      </c>
+      <c r="H42" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>83</v>
+        <v>34</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>89</v>
       </c>
       <c r="C43" t="s">
-        <v>2</v>
+        <v>90</v>
       </c>
       <c r="D43" t="s">
-        <v>84</v>
+        <v>60</v>
       </c>
       <c r="E43" t="s">
-        <v>85</v>
-      </c>
-      <c r="F43" t="s">
-        <v>86</v>
-      </c>
-      <c r="G43" t="s">
-        <v>87</v>
-      </c>
-      <c r="H43" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+        <v>91</v>
+      </c>
+      <c r="F43">
+        <v>0</v>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>34</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="C44" t="s">
-        <v>90</v>
-      </c>
-      <c r="D44" t="s">
-        <v>60</v>
-      </c>
-      <c r="E44" t="s">
-        <v>91</v>
-      </c>
-      <c r="F44">
-        <v>0</v>
-      </c>
-      <c r="G44">
-        <v>0</v>
-      </c>
-      <c r="H44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B45" s="3" t="s">
         <v>92</v>
       </c>
     </row>

--- a/plate3d/PLATE3D_HBASE.xlsx
+++ b/plate3d/PLATE3D_HBASE.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="94">
   <si>
     <t>HAUNCHED BOX BASE - every plate at its scheduled size, thickness and count</t>
   </si>
@@ -241,13 +241,16 @@
     <t>pl.hadd2_1</t>
   </si>
   <si>
-    <t>br</t>
+    <t>tl</t>
   </si>
   <si>
     <t>pl.hadd2_2</t>
   </si>
   <si>
     <t>pl.hadd1_1</t>
+  </si>
+  <si>
+    <t>tc</t>
   </si>
   <si>
     <t>BASE</t>
@@ -1615,13 +1618,13 @@
         <v>76</v>
       </c>
       <c r="F35">
-        <v>-71</v>
+        <v>71</v>
       </c>
       <c r="G35">
         <v>50</v>
       </c>
       <c r="H35">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="I35" t="s">
         <v>63</v>
@@ -1653,13 +1656,13 @@
         <v>76</v>
       </c>
       <c r="F36">
-        <v>-71</v>
+        <v>71</v>
       </c>
       <c r="G36">
         <v>-50</v>
       </c>
       <c r="H36">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="I36" t="s">
         <v>63</v>
@@ -1688,16 +1691,16 @@
         <v>78</v>
       </c>
       <c r="E37" t="s">
-        <v>31</v>
+        <v>79</v>
       </c>
       <c r="F37">
-        <v>-176</v>
+        <v>176</v>
       </c>
       <c r="G37">
         <v>0</v>
       </c>
       <c r="H37">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="I37" t="s">
         <v>66</v>
@@ -1723,13 +1726,13 @@
         <v>2</v>
       </c>
       <c r="D39" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E39" t="s">
         <v>52</v>
       </c>
       <c r="F39" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -1743,39 +1746,39 @@
         <v>60</v>
       </c>
       <c r="D40" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E40" t="s">
         <v>13</v>
       </c>
       <c r="F40" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C42" t="s">
         <v>2</v>
       </c>
       <c r="D42" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E42" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F42" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G42" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H42" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
@@ -1783,16 +1786,16 @@
         <v>34</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C43" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D43" t="s">
         <v>60</v>
       </c>
       <c r="E43" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F43">
         <v>0</v>
@@ -1809,7 +1812,7 @@
         <v>34</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>

--- a/plate3d/PLATE3D_HBASE.xlsx
+++ b/plate3d/PLATE3D_HBASE.xlsx
@@ -241,7 +241,7 @@
     <t>pl.hadd2_1</t>
   </si>
   <si>
-    <t>tl</t>
+    <t>tr</t>
   </si>
   <si>
     <t>pl.hadd2_2</t>
@@ -1618,7 +1618,7 @@
         <v>76</v>
       </c>
       <c r="F35">
-        <v>71</v>
+        <v>170</v>
       </c>
       <c r="G35">
         <v>50</v>
@@ -1656,7 +1656,7 @@
         <v>76</v>
       </c>
       <c r="F36">
-        <v>71</v>
+        <v>170</v>
       </c>
       <c r="G36">
         <v>-50</v>
@@ -1694,13 +1694,13 @@
         <v>79</v>
       </c>
       <c r="F37">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G37">
         <v>0</v>
       </c>
       <c r="H37">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="I37" t="s">
         <v>66</v>
